--- a/casos de prueba.xlsx
+++ b/casos de prueba.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\calculadora_impuestos-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F0CA6-1EF7-445B-BAE6-27E5A4DF86FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6723F7C7-EC83-4610-9CF8-B9DB93BD067F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de prueba" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>Documentacion de Pruebas - Calculadora de Impuestos de Venta</t>
   </si>
@@ -72,67 +77,10 @@
     <t>CP-02</t>
   </si>
   <si>
-    <t>Calculo de IVA del 5%</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema calcule correctamente el IVA del 5% sobre un producto gravado a esa tarifa.</t>
-  </si>
-  <si>
-    <t>Precio: 200000; Impuesto seleccionado: IVA 5%</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio del producto.
-2. Seleccionar IVA 5%.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema muestra IVA = 10000 y Total = 210000.</t>
-  </si>
-  <si>
     <t>CP-03</t>
   </si>
   <si>
-    <t>Producto exento de impuestos</t>
-  </si>
-  <si>
-    <t>Verificar que un producto marcado como exento no genere ningun valor de IVA.</t>
-  </si>
-  <si>
-    <t>El sistema permite marcar un producto como Exento.</t>
-  </si>
-  <si>
-    <t>Precio: 50000; Categoria: Exento</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio del producto.
-2. Seleccionar la categoria Exento.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema muestra IVA = 0 y Total = 50000 (igual al precio ingresado).</t>
-  </si>
-  <si>
     <t>CP-04</t>
-  </si>
-  <si>
-    <t>Producto excluido de impuestos</t>
-  </si>
-  <si>
-    <t>Verificar que un producto marcado como excluido no genere ningun valor de IVA.</t>
-  </si>
-  <si>
-    <t>El sistema permite marcar un producto como Excluido.</t>
-  </si>
-  <si>
-    <t>Precio: 75000; Categoria: Excluido</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio del producto.
-2. Seleccionar la categoria Excluido.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema muestra IVA = 0 y Total = 75000.</t>
   </si>
   <si>
     <t>CP-05</t>
@@ -161,47 +109,7 @@
     <t>CP-06</t>
   </si>
   <si>
-    <t>Producto con impuesto de rentas a los licores</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema calcule correctamente el impuesto a los licores sobre una bebida alcoholica.</t>
-  </si>
-  <si>
-    <t>El sistema tiene configurada la tarifa vigente del impuesto a los licores.</t>
-  </si>
-  <si>
-    <t>Precio: 60000; Categoria: Bebida alcoholica</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio del producto.
-2. Seleccionar la categoria de licores.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema muestra el valor del impuesto a los licores calculado y discriminado del total.</t>
-  </si>
-  <si>
     <t>CP-07</t>
-  </si>
-  <si>
-    <t>Producto con impuesto a las bolsas plasticas</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema calcule correctamente el impuesto a las bolsas plasticas cuando aplica.</t>
-  </si>
-  <si>
-    <t>El sistema permite marcar el uso de bolsas plasticas en la compra.</t>
-  </si>
-  <si>
-    <t>Precio: 30000; Bolsas plasticas: Si (cantidad 2)</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio del producto.
-2. Marcar la opcion de bolsas plasticas.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema suma el impuesto a las bolsas plasticas al total, mostrandolo como rubro independiente.</t>
   </si>
   <si>
     <t>CP-08</t>
@@ -231,75 +139,10 @@
     <t>CP-09</t>
   </si>
   <si>
-    <t>Combinacion permitida: impuesto a licores + impuesto a bolsas</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema permita combinar el impuesto a los licores con el impuesto a las bolsas plasticas.</t>
-  </si>
-  <si>
-    <t>El producto es una bebida alcoholica y la compra incluye bolsas plasticas.</t>
-  </si>
-  <si>
-    <t>Precio: 60000; Categoria: Licores; Bolsas plasticas: Si</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio.
-2. Seleccionar categoria de licores.
-3. Marcar bolsas plasticas.
-4. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema muestra el impuesto a licores y el impuesto a bolsas discriminados por separado en el total.</t>
-  </si>
-  <si>
     <t>CP-10</t>
   </si>
   <si>
-    <t>Precio con valores decimales</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema calcule correctamente los impuestos cuando el precio incluye decimales.</t>
-  </si>
-  <si>
-    <t>El sistema acepta valores decimales en el campo de precio.</t>
-  </si>
-  <si>
-    <t>Precio: 19999.99; Impuesto seleccionado: IVA 19%</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio con decimales.
-2. Seleccionar IVA 19%.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema calcula el IVA sobre el valor decimal exacto y presenta el resultado redondeado a 2 decimales.</t>
-  </si>
-  <si>
-    <t>Validacion del calculo del total de la compra</t>
-  </si>
-  <si>
-    <t>Verificar que el total mostrado corresponda a la suma exacta del precio base mas todos los impuestos aplicables.</t>
-  </si>
-  <si>
-    <t>Se cuenta con un producto con dos impuestos aplicables (IVA 19% y bolsas plasticas).</t>
-  </si>
-  <si>
-    <t>Precio: 120000; Impuesto: IVA 19%; Bolsas plasticas: Si</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio.
-2. Seleccionar IVA 19% y bolsas plasticas.
-3. Ejecutar el calculo.
-4. Verificar el total mostrado.</t>
-  </si>
-  <si>
-    <t>El total mostrado es igual al precio base mas la suma de cada impuesto discriminado, sin diferencias de redondeo.</t>
-  </si>
-  <si>
     <t>CASOS EXCEPCIONALES</t>
-  </si>
-  <si>
-    <t>CP-11</t>
   </si>
   <si>
     <t>Precio muy alto (limite superior aceptado)</t>
@@ -322,33 +165,7 @@
     <t>El sistema procesa el calculo sin errores de desbordamiento y muestra el total correctamente.</t>
   </si>
   <si>
-    <t>CP-12</t>
-  </si>
-  <si>
-    <t>Precio muy pequeno (limite inferior aceptado)</t>
-  </si>
-  <si>
-    <t>Verificar el comportamiento del sistema al procesar un precio muy cercano a cero pero valido.</t>
-  </si>
-  <si>
-    <t>El sistema tiene definido un valor minimo de precio permitido mayor que cero.</t>
-  </si>
-  <si>
-    <t>Precio: 1; Impuesto seleccionado: IVA 19%</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio minimo permitido.
-2. Seleccionar IVA 19%.
-3. Ejecutar el calculo.</t>
-  </si>
-  <si>
-    <t>El sistema calcula el impuesto correspondiente sin generar errores de redondeo o precision.</t>
-  </si>
-  <si>
     <t>CASOS DE ERROR</t>
-  </si>
-  <si>
-    <t>CP-13</t>
   </si>
   <si>
     <t>Precio negativo</t>
@@ -371,24 +188,105 @@
     <t>El sistema no realiza el calculo y muestra un mensaje de error indicando que el precio debe ser mayor que cero.</t>
   </si>
   <si>
-    <t>CP-14</t>
-  </si>
-  <si>
-    <t>Precio igual a cero</t>
-  </si>
-  <si>
-    <t>Verificar que el sistema rechace un precio igual a cero.</t>
-  </si>
-  <si>
-    <t>Precio: 0; Impuesto seleccionado: IVA 19%</t>
-  </si>
-  <si>
-    <t>1. Ingresar el precio en 0.
+    <t>No seleccionar ningun tipo de impuesto</t>
+  </si>
+  <si>
+    <t>Verificar el comportamiento del sistema cuando no se selecciona ninguna categoria de impuesto.</t>
+  </si>
+  <si>
+    <t>El sistema requiere que se seleccione una categoria de impuesto antes de calcular.</t>
+  </si>
+  <si>
+    <t>Precio: 50000; Impuesto seleccionado: ninguno</t>
+  </si>
+  <si>
+    <t>El sistema muestra un mensaje solicitando seleccionar al menos una categoria de impuesto y no ejecuta el calculo.</t>
+  </si>
+  <si>
+    <t>1. Ingresar el precio.
+2. No seleccionar ningun impuesto.
+3. Intentar ejecutar el calculo.</t>
+  </si>
+  <si>
+    <t>Campo de precio vacio</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema no permita ejecutar el calculo si el campo de precio esta vacio.</t>
+  </si>
+  <si>
+    <t>El sistema valida que el campo de precio sea obligatorio.</t>
+  </si>
+  <si>
+    <t>Precio: (campo vacio); Impuesto seleccionado: IVA 19%</t>
+  </si>
+  <si>
+    <t>1. Dejar el campo de precio vacio.
 2. Seleccionar IVA 19%.
 3. Intentar ejecutar el calculo.</t>
   </si>
   <si>
-    <t>CP-15</t>
+    <t>El sistema muestra un mensaje de error indicando que el precio es obligatorio y no ejecuta el calculo.</t>
+  </si>
+  <si>
+    <t>Letras en el campo de precio</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema rechace texto alfabetico ingresado en el campo de precio.</t>
+  </si>
+  <si>
+    <t>El sistema valida que el campo de precio solo acepte valores numericos.</t>
+  </si>
+  <si>
+    <t>Precio: 'abc'; Impuesto seleccionado: IVA 19%</t>
+  </si>
+  <si>
+    <t>1. Ingresar letras en el campo de precio.
+2. Seleccionar IVA 19%.
+3. Intentar ejecutar el calculo.</t>
+  </si>
+  <si>
+    <t>El sistema muestra un mensaje de error indicando que el precio debe ser numerico y no ejecuta el calculo.</t>
+  </si>
+  <si>
+    <t>Seleccion simultanea de IVA 5% y 19%</t>
+  </si>
+  <si>
+    <t>Verificar que el sistema no permita seleccionar dos tarifas de IVA distintas para un mismo producto.</t>
+  </si>
+  <si>
+    <t>El sistema restringe la seleccion a un unico tipo de IVA por producto.</t>
+  </si>
+  <si>
+    <t>Precio: 100000; Impuestos seleccionados: IVA 5% e IVA 19% al mismo tiempo</t>
+  </si>
+  <si>
+    <t>1. Ingresar el precio.
+2. Marcar simultaneamente IVA 5% e IVA 19%.
+3. Intentar ejecutar el calculo.</t>
+  </si>
+  <si>
+    <t>El sistema impide la seleccion simultanea y muestra un mensaje indicando que solo puede aplicarse un IVA por producto.</t>
+  </si>
+  <si>
+    <t>Impuesto de bolsas aplicado a un producto excluido</t>
+  </si>
+  <si>
+    <t>Verificar el comportamiento del sistema cuando se intenta aplicar el impuesto a bolsas plasticas a un producto marcado como excluido de IVA.</t>
+  </si>
+  <si>
+    <t>El producto esta marcado como Excluido y se activa la opcion de bolsas plasticas.</t>
+  </si>
+  <si>
+    <t>Precio: 40000; Categoria: Excluido; Bolsas plasticas: Si</t>
+  </si>
+  <si>
+    <t>1. Ingresar el precio.
+2. Seleccionar la categoria Excluido.
+3. Marcar bolsas plasticas.
+4. Ejecutar el calculo.</t>
+  </si>
+  <si>
+    <t>El sistema calcula el impuesto a bolsas de forma independiente al IVA, ya que este ultimo no aplica a productos excluidos; el IVA permanece en 0.</t>
   </si>
 </sst>
 </file>
@@ -408,27 +306,32 @@
       <sz val="14"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -508,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -522,6 +425,21 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -546,11 +464,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,30 +780,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -942,379 +855,398 @@
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="B6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>20</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="B12" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="B15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="B16" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B17" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="B18" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="C18" s="21" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="D18" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="E18" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="F18" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G18" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="19" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
